--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_B154_Playwright_Py\b154_afw\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03966074-5BBA-4127-8EC2-58AFBF224963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CF1D98-A4BF-4908-BD85-C326A3F4A191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="test_1" sheetId="1" r:id="rId1"/>
+    <sheet name="ValidLogin" sheetId="1" r:id="rId1"/>
+    <sheet name="InvalidLogin" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,12 +26,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>username</t>
   </si>
   <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>student123</t>
+  </si>
+  <si>
+    <t>akshara123</t>
+  </si>
+  <si>
     <t>bhanu</t>
+  </si>
+  <si>
+    <t>bhanu123</t>
   </si>
 </sst>
 </file>
@@ -348,17 +361,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{565810F3-47BC-485F-9D06-E7EDF447C5E1}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
